--- a/final apps/HR/UAT/UAT_HR_TestScript.xlsx
+++ b/final apps/HR/UAT/UAT_HR_TestScript.xlsx
@@ -32,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,11 +65,6 @@
     <font>
       <b val="1"/>
       <color rgb="001A7F5A"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B71C1C"/>
       <sz val="12"/>
     </font>
     <font>
@@ -136,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,11 +141,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -575,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G39"/>
+  <dimension ref="B2:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -769,283 +763,299 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Known issues (do not log as new defects)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>- Employees list may show 0 rows even though employees exist in the database — known issue under investigation; mark affected cases Blocked and note it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Seeded UAT data (your starting point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>- 5 active employees incl. E1101 Mohammed Al Mansoori, E1102 Fatima Al Hosani, E1103 Omar Khalil (seeded).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>- Documents seeded with expiries ~20 / ~45 days (compliance list + badge data) and one ~13 months out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>- HR roles: SHAIKHA.GALAMERI = HR_MANAGER, SHAIKHA.ALSUWAIDI = HR_VIEWER.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Live summary</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Functional area</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Executed %</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="12" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Access &amp; Session</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C34" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D34" s="11">
         <f>COUNTIF('Access &amp; Session'!F:F,"Pass")</f>
         <v/>
       </c>
-      <c r="E32" s="12">
+      <c r="E34" s="11">
         <f>COUNTIF('Access &amp; Session'!F:F,"Fail")</f>
         <v/>
       </c>
-      <c r="F32" s="12">
+      <c r="F34" s="11">
         <f>COUNTIF('Access &amp; Session'!F:F,"Blocked")</f>
         <v/>
       </c>
-      <c r="G32" s="12">
-        <f>ROUND(COUNTA('Access &amp; Session'!F2:F500)/C32*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="12" t="inlineStr">
+      <c r="G34" s="11">
+        <f>ROUND(COUNTA('Access &amp; Session'!F2:F500)/C34*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C35" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D35" s="11">
         <f>COUNTIF('Dashboard'!F:F,"Pass")</f>
         <v/>
       </c>
-      <c r="E33" s="12">
+      <c r="E35" s="11">
         <f>COUNTIF('Dashboard'!F:F,"Fail")</f>
         <v/>
       </c>
-      <c r="F33" s="12">
+      <c r="F35" s="11">
         <f>COUNTIF('Dashboard'!F:F,"Blocked")</f>
         <v/>
       </c>
-      <c r="G33" s="12">
-        <f>ROUND(COUNTA('Dashboard'!F2:F500)/C33*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="12" t="inlineStr">
+      <c r="G35" s="11">
+        <f>ROUND(COUNTA('Dashboard'!F2:F500)/C35*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C36" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D36" s="11">
         <f>COUNTIF('People'!F:F,"Pass")</f>
         <v/>
       </c>
-      <c r="E34" s="12">
+      <c r="E36" s="11">
         <f>COUNTIF('People'!F:F,"Fail")</f>
         <v/>
       </c>
-      <c r="F34" s="12">
+      <c r="F36" s="11">
         <f>COUNTIF('People'!F:F,"Blocked")</f>
         <v/>
       </c>
-      <c r="G34" s="12">
-        <f>ROUND(COUNTA('People'!F2:F500)/C34*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="12" t="inlineStr">
+      <c r="G36" s="11">
+        <f>ROUND(COUNTA('People'!F2:F500)/C36*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C37" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D37" s="11">
         <f>COUNTIF('Structure'!F:F,"Pass")</f>
         <v/>
       </c>
-      <c r="E35" s="12">
+      <c r="E37" s="11">
         <f>COUNTIF('Structure'!F:F,"Fail")</f>
         <v/>
       </c>
-      <c r="F35" s="12">
+      <c r="F37" s="11">
         <f>COUNTIF('Structure'!F:F,"Blocked")</f>
         <v/>
       </c>
-      <c r="G35" s="12">
-        <f>ROUND(COUNTA('Structure'!F2:F500)/C35*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="12" t="inlineStr">
+      <c r="G37" s="11">
+        <f>ROUND(COUNTA('Structure'!F2:F500)/C37*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C38" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D38" s="11">
         <f>COUNTIF('Compliance'!F:F,"Pass")</f>
         <v/>
       </c>
-      <c r="E36" s="12">
+      <c r="E38" s="11">
         <f>COUNTIF('Compliance'!F:F,"Fail")</f>
         <v/>
       </c>
-      <c r="F36" s="12">
+      <c r="F38" s="11">
         <f>COUNTIF('Compliance'!F:F,"Blocked")</f>
         <v/>
       </c>
-      <c r="G36" s="12">
-        <f>ROUND(COUNTA('Compliance'!F2:F500)/C36*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="12" t="inlineStr">
+      <c r="G38" s="11">
+        <f>ROUND(COUNTA('Compliance'!F2:F500)/C38*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Administration</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C39" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D39" s="11">
         <f>COUNTIF('Administration'!F:F,"Pass")</f>
         <v/>
       </c>
-      <c r="E37" s="12">
+      <c r="E39" s="11">
         <f>COUNTIF('Administration'!F:F,"Fail")</f>
         <v/>
       </c>
-      <c r="F37" s="12">
+      <c r="F39" s="11">
         <f>COUNTIF('Administration'!F:F,"Blocked")</f>
         <v/>
       </c>
-      <c r="G37" s="12">
-        <f>ROUND(COUNTA('Administration'!F2:F500)/C37*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="12" t="inlineStr">
+      <c r="G39" s="11">
+        <f>ROUND(COUNTA('Administration'!F2:F500)/C39*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Shell &amp; Language</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C40" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D40" s="11">
         <f>COUNTIF('Shell &amp; Language'!F:F,"Pass")</f>
         <v/>
       </c>
-      <c r="E38" s="12">
+      <c r="E40" s="11">
         <f>COUNTIF('Shell &amp; Language'!F:F,"Fail")</f>
         <v/>
       </c>
-      <c r="F38" s="12">
+      <c r="F40" s="11">
         <f>COUNTIF('Shell &amp; Language'!F:F,"Blocked")</f>
         <v/>
       </c>
-      <c r="G38" s="12">
-        <f>ROUND(COUNTA('Shell &amp; Language'!F2:F500)/C38*100,0)&amp;"%"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="13" t="inlineStr">
+      <c r="G40" s="11">
+        <f>ROUND(COUNTA('Shell &amp; Language'!F2:F500)/C40*100,0)&amp;"%"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C39" s="13">
-        <f>SUM(C32:C38)</f>
-        <v/>
-      </c>
-      <c r="D39" s="13">
-        <f>SUM(D32:D38)</f>
-        <v/>
-      </c>
-      <c r="E39" s="13">
-        <f>SUM(E32:E38)</f>
-        <v/>
-      </c>
-      <c r="F39" s="13">
-        <f>SUM(F32:F38)</f>
+      <c r="C41" s="12">
+        <f>SUM(C34:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="12">
+        <f>SUM(D34:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="12">
+        <f>SUM(E34:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="12">
+        <f>SUM(F34:F40)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="B28:G28"/>
+  <mergeCells count="20">
     <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C10:G10"/>
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="B17:G17"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="C23:G23"/>
     <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="B30:G30"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="B15:G15"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1072,114 +1082,114 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>HR-ACC-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Shared session</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Entry from Admin</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Login in Admin
 2. Switch to HR via the module dropdown</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>HR opens logged-in; viewer/manager/admin nav per role</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr"/>
-      <c r="G2" s="17" t="inlineStr"/>
-      <c r="H2" s="17" t="inlineStr"/>
-      <c r="I2" s="16" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>HR-ACC-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>No session</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Direct open without login</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Fresh private window &gt; HR URL</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Redirected to Admin login</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
-      <c r="H3" s="17" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I3"/>
@@ -1227,113 +1237,113 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>HR-DSH-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Headcount cards</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open HR Dashboard</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Cards (headcount, vacancies, expiring docs) show live values</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr"/>
-      <c r="G2" s="17" t="inlineStr"/>
-      <c r="H2" s="17" t="inlineStr"/>
-      <c r="I2" s="16" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>HR-DSH-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Charts</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Headcount + expiry horizon</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Wait for both charts</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Approved vs filled headcount chart + document expiry horizon chart render</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
-      <c r="H3" s="17" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I3"/>
@@ -1381,305 +1391,305 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>HR-EMP-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Employees list</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Paged list</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open Employees
 2. Page next/previous</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Employee cards/rows with photo or initials; paging works without losing filters</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr"/>
-      <c r="G2" s="17" t="inlineStr"/>
-      <c r="H2" s="17" t="inlineStr"/>
-      <c r="I2" s="16" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>HR-EMP-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Employees list</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Search + filters</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Search by name
 2. Filter by organisation and grade</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Server-side filtering; combined filters work; clear restores</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
-      <c r="H3" s="17" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>HR-EMP-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Employee detail</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Full record</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Open an employee</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Personal, job (position/grade/org), contacts, documents tabs all populated</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr"/>
-      <c r="G4" s="17" t="inlineStr"/>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="16" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>HR-EMP-04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>New employee</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>1. New Employee: number, names EN/AR, hire date, position, org, grade
 2. Save</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Employee created and findable; appears in headcount</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr"/>
-      <c r="G5" s="17" t="inlineStr"/>
-      <c r="H5" s="17" t="inlineStr"/>
-      <c r="I5" s="16" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>HR-EMP-05</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Edit</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Update employee</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>1. Edit job title / phone / org
 2. Save and reopen</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Changes persist</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr"/>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr"/>
+      <c r="H6" s="16" t="inlineStr"/>
+      <c r="I6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>HR-EMP-06</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Upload employee photo</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>1. In employee detail click photo/upload
 2. Choose an image</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Picker opens; photo saved and shown in list + detail (small file &lt; 20KB if large files fail)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr"/>
+      <c r="H7" s="16" t="inlineStr"/>
+      <c r="I7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>HR-EMP-07</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Add employee document</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>1. Add a document (type, number, expiry date) to an employee
 2. Upload the file</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Document listed with expiry; appears in compliance views</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>HR-EMP-08</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Org hierarchy</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Org chart</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>1. Open Org Hierarchy</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Tree/chart of org units with employees; expand/collapse works</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-      <c r="H9" s="17" t="inlineStr"/>
-      <c r="I9" s="16" t="inlineStr"/>
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr"/>
+      <c r="H9" s="16" t="inlineStr"/>
+      <c r="I9" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I9"/>
@@ -1727,69 +1737,69 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>HR-STR-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Positions</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open Positions
 2. Create a position (title, org, grade, headcount)
@@ -1797,111 +1807,111 @@
 4. Try assigning an employee to it</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Position created/edited; assignable to employees; filled count updates</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr"/>
-      <c r="G2" s="17" t="inlineStr"/>
-      <c r="H2" s="17" t="inlineStr"/>
-      <c r="I2" s="16" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>HR-STR-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Jobs</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Open Jobs
 2. Create/edit a job</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Job persists; selectable on positions/employees</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
-      <c r="H3" s="17" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>HR-STR-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Grades</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>List + edit</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Open Grades
 2. Edit a grade label</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Grades listed; edit persists; grade dropdowns reflect it</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr"/>
-      <c r="G4" s="17" t="inlineStr"/>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="16" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>HR-STR-04</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Locations</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>1. Open Locations
 2. Add/edit a location</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Location persists; selectable on employees/positions</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr"/>
-      <c r="G5" s="17" t="inlineStr"/>
-      <c r="H5" s="17" t="inlineStr"/>
-      <c r="I5" s="16" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
+      <c r="H5" s="16" t="inlineStr"/>
+      <c r="I5" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I5"/>
@@ -1949,145 +1959,145 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>HR-CMP-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Expiring documents</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Expiry list + badge</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open Documents (compliance)
 2. Compare the side-nav badge number with rows</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Documents expiring within the window listed with days-left; badge matches</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr"/>
-      <c r="G2" s="17" t="inlineStr"/>
-      <c r="H2" s="17" t="inlineStr"/>
-      <c r="I2" s="16" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>HR-CMP-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Document detail</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Navigate to employee</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Click an expiring document</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Opens the owning employee's documents tab</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
-      <c r="H3" s="17" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>HR-CMP-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Renewal</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Update expiry</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Update a document's expiry to a future date</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Item leaves the expiring list; badge decreases</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr"/>
-      <c r="G4" s="17" t="inlineStr"/>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="16" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
@@ -2135,115 +2145,115 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>HR-ADM-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Lookups</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>HR lookup values</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Open Lookups
 2. Add/edit a value in an HR category</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Value persists and appears in the matching dropdowns</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr"/>
-      <c r="G2" s="17" t="inlineStr"/>
-      <c r="H2" s="17" t="inlineStr"/>
-      <c r="I2" s="16" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>HR-ADM-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Module settings</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>HR settings</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Open Module Settings
 2. Edit a value and refresh</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Persists; no errors</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
-      <c r="H3" s="17" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I3"/>
@@ -2291,145 +2301,145 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Function</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Tested By</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Test Date</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Comments / Defect Ref</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>HR-SHL-01</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Switcher</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Cross-module hop</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>1. Module dropdown &gt; Admin and back</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>No re-login</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr"/>
-      <c r="G2" s="17" t="inlineStr"/>
-      <c r="H2" s="17" t="inlineStr"/>
-      <c r="I2" s="16" t="inlineStr"/>
+      <c r="F2" s="16" t="inlineStr"/>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+      <c r="I2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>HR-SHL-02</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Arabic</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>RTL pass</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>1. Switch to AR
 2. Walk Employees + Dashboard</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Mirrored layout; Arabic shell; Arabic names display correctly; Latin digits</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
-      <c r="G3" s="17" t="inlineStr"/>
-      <c r="H3" s="17" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+      <c r="I3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>HR-SHL-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>HR notifications</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>1. Check the bell after document-expiry alerts run</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Expiry notifications visible and readable</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr"/>
-      <c r="G4" s="17" t="inlineStr"/>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="16" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+      <c r="I4" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
